--- a/data/trans_bre/P36BPD07_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P36BPD07_R-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,49%</t>
+          <t>-3,44%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 13,37</t>
+          <t>0,87; 13,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 8,37</t>
+          <t>-12,98; 7,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 21,29</t>
+          <t>1,36; 21,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 13,76</t>
+          <t>-18,8; 13,08</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,26</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,89</t>
+          <t>-3,44; 6,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 27,09</t>
+          <t>3,56; 17,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 9,57</t>
+          <t>-4,41; 8,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 47,57</t>
+          <t>5,34; 28,91</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,7</t>
+          <t>-5,61; 3,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 7,3</t>
+          <t>-2,33; 7,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 3,39</t>
+          <t>-6,7; 3,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,87</t>
+          <t>-3,23; 11,25</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,74</t>
+          <t>0,11; 7,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 8,05</t>
+          <t>0,79; 9,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 9,32</t>
+          <t>0,14; 8,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 11,45</t>
+          <t>1,08; 14,52</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,6</t>
+          <t>-4,41; 1,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,46</t>
+          <t>1,17; 9,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,69</t>
+          <t>-4,56; 1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,95</t>
+          <t>1,53; 13,36</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,3</t>
+          <t>-1,32; 3,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 17,78</t>
+          <t>-1,41; 7,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,48</t>
+          <t>-1,35; 3,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 23,38</t>
+          <t>-1,69; 9,73</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,11</t>
+          <t>-2,8; 3,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,6</t>
+          <t>0,9; 9,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 3,29</t>
+          <t>-2,86; 3,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,14</t>
+          <t>1,04; 12,51</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,23</t>
+          <t>0,64; 3,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 9,2</t>
+          <t>2,74; 6,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,04</t>
+          <t>0,74; 4,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 12,73</t>
+          <t>3,77; 9,94</t>
         </is>
       </c>
     </row>
